--- a/research_methodology.xlsx
+++ b/research_methodology.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpardo/Desktop/Relation_low_resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpardo/Desktop/PhD Tesis/Relation_low_resources/re_te_lowresources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDB3D77-C6BC-B043-973E-DE2FE022B367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9364DF-FA24-AC4A-A994-C29ACBA4F03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3440" yWindow="500" windowWidth="30160" windowHeight="20500" activeTab="7" xr2:uid="{C9EDA97C-CF5E-1244-9D11-D7F0F55965F3}"/>
+    <workbookView xWindow="3440" yWindow="500" windowWidth="30160" windowHeight="20500" activeTab="11" xr2:uid="{C9EDA97C-CF5E-1244-9D11-D7F0F55965F3}"/>
   </bookViews>
   <sheets>
     <sheet name="RQs" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="450">
   <si>
     <t>RQ</t>
   </si>
@@ -287,12 +287,6 @@
     <t>What are the main challenges facing relation extraction approaches in data-scarce environments? What techniques can mitigate these limitations?</t>
   </si>
   <si>
-    <t>Generica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se basa mas en herramientas, metodologias.  Muy dificil de comprobar. No hay nuevas arquitecturas encoders mientras los decoders cada dia son mas grandes o hay mas investigacion. </t>
-  </si>
-  <si>
     <t>Distant supervision</t>
   </si>
   <si>
@@ -332,9 +326,6 @@
     <t>Accepted</t>
   </si>
   <si>
-    <t>Lingusitico</t>
-  </si>
-  <si>
     <t>ID R1</t>
   </si>
   <si>
@@ -1244,9 +1235,6 @@
     <t>Only partial text</t>
   </si>
   <si>
-    <t>Tablas encasillando caracteristicas comunes de los papers</t>
-  </si>
-  <si>
     <t>characteristics</t>
   </si>
   <si>
@@ -1445,9 +1433,6 @@
     <t>Without duplicates</t>
   </si>
   <si>
-    <t>Parece que todos, pero revisar.</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
@@ -1467,6 +1452,18 @@
   </si>
   <si>
     <t>Training</t>
+  </si>
+  <si>
+    <t>Relation &gt; surveys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is based more on tools and methodologies.  Very difficult to verify. There are no new encoder architectures, while decoders are getting bigger every day and there is more research. </t>
+  </si>
+  <si>
+    <t>Generic</t>
+  </si>
+  <si>
+    <t>Lingusitical</t>
   </si>
 </sst>
 </file>
@@ -1925,15 +1922,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1943,8 +1931,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2350,7 +2347,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="66" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -2367,7 +2364,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -2381,7 +2378,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>57</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -2395,7 +2392,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="63" t="s">
-        <v>58</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2454,7 +2451,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5"/>
     </row>
@@ -2473,7 +2470,7 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H11" s="16"/>
       <c r="I11" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -2483,7 +2480,7 @@
       <c r="D12" s="27"/>
       <c r="H12" s="17"/>
       <c r="I12" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -2493,7 +2490,7 @@
       <c r="D13" s="21"/>
       <c r="H13" s="18"/>
       <c r="I13" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -2923,19 +2920,19 @@
         <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>27</v>
@@ -2951,16 +2948,16 @@
         <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="K2" s="62" t="s">
         <v>34</v>
@@ -2976,16 +2973,16 @@
         <v>40</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H3" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>41</v>
@@ -3018,24 +3015,24 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="G8" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L8" s="97" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="M8" s="97"/>
       <c r="N8" s="28" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="O8" s="2"/>
       <c r="S8" s="9"/>
@@ -3059,7 +3056,7 @@
         <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G9" s="62" t="s">
         <v>33</v>
@@ -3068,25 +3065,25 @@
         <v>40</v>
       </c>
       <c r="I9" s="62" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J9" s="62" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K9" s="62" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="28" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="M9" s="28" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="O9" s="62" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3232,7 +3229,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="67" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="67"/>
       <c r="C1" s="67"/>
@@ -3246,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>8</v>
@@ -3271,13 +3268,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" s="5">
         <v>2.2999999999999998</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -3285,49 +3282,49 @@
         <v>3</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" s="68" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" s="69"/>
       <c r="D6" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" s="70"/>
       <c r="D7" s="5" t="s">
-        <v>72</v>
+        <v>449</v>
       </c>
       <c r="F7" s="18"/>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -3375,71 +3372,71 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="67" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B1" s="67"/>
       <c r="C1" s="72" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="75" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B2" s="75"/>
       <c r="C2" s="73" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D2" s="73"/>
     </row>
     <row r="3" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="75" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B3" s="75"/>
       <c r="C3" s="73" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D3" s="73"/>
     </row>
     <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="75" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B4" s="75"/>
       <c r="C4" s="74" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D4" s="74"/>
     </row>
     <row r="5" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="75" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B5" s="75"/>
       <c r="C5" s="73" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D5" s="73"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="75" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B6" s="75"/>
       <c r="C6" s="73" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D6" s="73"/>
     </row>
     <row r="7" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="71" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B7" s="71"/>
       <c r="C7" s="71" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D7" s="71"/>
     </row>
@@ -3477,11 +3474,11 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="76" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="77" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D1" s="77"/>
     </row>
@@ -3490,41 +3487,41 @@
         <v>18</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C2" s="28" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>333</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -3547,838 +3544,838 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B1" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>90</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C15" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B18" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B22" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C23" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C25" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B26" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C27" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B28" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B29" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C29" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B30" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C31" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B37" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C37" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C38" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B39" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C39" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C40" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C41" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B43" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C43" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B44" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C44" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B45" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B46" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C46" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B47" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C47" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B48" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B49" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B50" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C51" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B52" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C52" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B53" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C53" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B54" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C54" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B55" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C55" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B56" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C56" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B57" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C57" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B58" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C58" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B59" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C59" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C60" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C61" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B62" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C62" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B63" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C63" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B64" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C64" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B65" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C65" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B66" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C66" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B67" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C67" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B68" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C68" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B69" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C69" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B70" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C70" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B71" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C71" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B72" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C72" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B73" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C73" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B74" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C74" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B75" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C75" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B76" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C76" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -4405,101 +4402,101 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" s="67" t="s">
-        <v>341</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="81" t="s">
-        <v>319</v>
-      </c>
-      <c r="E1" s="82"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="81" t="s">
-        <v>348</v>
-      </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="78" t="s">
-        <v>362</v>
-      </c>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78" t="s">
-        <v>369</v>
-      </c>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
+        <v>338</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="78" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="78" t="s">
+        <v>345</v>
+      </c>
+      <c r="H1" s="79"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="81" t="s">
+        <v>359</v>
+      </c>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81" t="s">
+        <v>366</v>
+      </c>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B2" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>93</v>
-      </c>
       <c r="D2" s="29" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G2" s="29" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J2" s="29" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K2" s="29" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="M2" s="29" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="N2" s="29" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O2" s="33" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="P2" s="29" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="Q2" s="29" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="R2" s="33" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D3" s="31">
         <v>24</v>
@@ -4554,13 +4551,13 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -4615,13 +4612,13 @@
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -4676,13 +4673,13 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -4737,13 +4734,13 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -4798,13 +4795,13 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D8" s="30">
         <v>0</v>
@@ -4859,13 +4856,13 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D9" s="30">
         <v>0</v>
@@ -4920,13 +4917,13 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D10" s="30">
         <v>0</v>
@@ -4981,13 +4978,13 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D11" s="31">
         <v>14</v>
@@ -5040,18 +5037,18 @@
         <v>25</v>
       </c>
       <c r="AI11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -5106,13 +5103,13 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -5167,13 +5164,13 @@
     </row>
     <row r="14" spans="1:35" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D14" s="30">
         <v>0</v>
@@ -5228,13 +5225,13 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D15" s="30">
         <v>0</v>
@@ -5289,13 +5286,13 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D16" s="30">
         <v>0</v>
@@ -5350,13 +5347,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D17" s="30">
         <v>0</v>
@@ -5411,13 +5408,13 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D18" s="30">
         <v>0</v>
@@ -5472,13 +5469,13 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D19" s="30">
         <v>0</v>
@@ -5533,13 +5530,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D20" s="30">
         <v>0</v>
@@ -5594,13 +5591,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D21" s="30">
         <v>0</v>
@@ -5655,13 +5652,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D22" s="30">
         <v>0</v>
@@ -5778,47 +5775,47 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D24" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F24" s="41"/>
       <c r="G24" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H24" s="40" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I24">
         <f>F23+I23</f>
         <v>587</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="K24" s="40" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="L24" s="32">
         <f>F23+I23+L23</f>
         <v>644</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="N24" s="40" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="O24" s="32">
         <f>F23+I23+L23+O23</f>
         <v>1123</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q24" s="40" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R24" s="32">
         <f>F23+I23+L23+O23+R23</f>
@@ -5828,7 +5825,7 @@
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B25" s="9"/>
       <c r="C25" s="36" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -5842,39 +5839,39 @@
       <c r="H25" s="2">
         <v>15</v>
       </c>
-      <c r="J25" s="80" t="s">
-        <v>435</v>
-      </c>
-      <c r="K25" s="80"/>
-      <c r="M25" s="80" t="s">
-        <v>435</v>
-      </c>
-      <c r="N25" s="80"/>
-      <c r="P25" s="80" t="s">
-        <v>435</v>
-      </c>
-      <c r="Q25" s="80"/>
+      <c r="J25" s="84" t="s">
+        <v>431</v>
+      </c>
+      <c r="K25" s="84"/>
+      <c r="M25" s="84" t="s">
+        <v>431</v>
+      </c>
+      <c r="N25" s="84"/>
+      <c r="P25" s="84" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q25" s="84"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="H26" s="56" t="s">
-        <v>433</v>
-      </c>
-      <c r="J26" s="79" t="s">
-        <v>434</v>
-      </c>
-      <c r="K26" s="79"/>
-      <c r="M26" s="80" t="s">
-        <v>371</v>
-      </c>
-      <c r="N26" s="80"/>
-      <c r="P26" s="80" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q26" s="80"/>
+        <v>429</v>
+      </c>
+      <c r="J26" s="83" t="s">
+        <v>430</v>
+      </c>
+      <c r="K26" s="83"/>
+      <c r="M26" s="84" t="s">
+        <v>368</v>
+      </c>
+      <c r="N26" s="84"/>
+      <c r="P26" s="84" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q26" s="84"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D27" s="72" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E27" s="72"/>
       <c r="F27" s="72"/>
@@ -5885,31 +5882,31 @@
       <c r="K27" s="72"/>
       <c r="L27" s="72"/>
     </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>446</v>
+      </c>
+    </row>
     <row r="51" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A51" s="12"/>
       <c r="B51" s="13" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" s="37"/>
       <c r="B52" s="13" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="38"/>
       <c r="B53" s="13" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D27:L27"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="A1:C1"/>
     <mergeCell ref="P1:R1"/>
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="M25:N25"/>
@@ -5918,6 +5915,11 @@
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="M1:O1"/>
+    <mergeCell ref="D27:L27"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5936,59 +5938,59 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="67" t="s">
-        <v>341</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="81" t="s">
-        <v>369</v>
-      </c>
-      <c r="E1" s="82"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="78" t="s">
-        <v>370</v>
-      </c>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+        <v>338</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="78" t="s">
+        <v>366</v>
+      </c>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="81" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B2" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>93</v>
-      </c>
       <c r="D2" s="29" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G2" s="29" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D3" s="31">
         <v>24</v>
@@ -6013,13 +6015,13 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -6044,13 +6046,13 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -6075,13 +6077,13 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D6" s="2">
         <v>2</v>
@@ -6106,13 +6108,13 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -6137,13 +6139,13 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -6168,13 +6170,13 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -6199,13 +6201,13 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D10" s="44">
         <v>0</v>
@@ -6227,17 +6229,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="84" t="s">
-        <v>428</v>
-      </c>
-      <c r="K10" s="84"/>
-      <c r="L10" s="84"/>
+      <c r="J10" s="82" t="s">
+        <v>424</v>
+      </c>
+      <c r="K10" s="82"/>
+      <c r="L10" s="82"/>
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="42" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D11" s="51">
         <f t="shared" ref="D11:I11" si="2">SUM(D3:D10)</f>
@@ -6269,12 +6271,12 @@
       </c>
       <c r="K11" s="94"/>
       <c r="L11" s="85" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="42" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
@@ -6295,7 +6297,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="50" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
@@ -6321,10 +6323,10 @@
       <c r="E14" s="55"/>
       <c r="F14" s="55"/>
       <c r="I14" s="88" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="K14" s="59">
         <f>J13-L14</f>
@@ -6337,7 +6339,7 @@
     <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="I15" s="89"/>
       <c r="J15" s="57" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="K15" s="61">
         <v>159</v>
@@ -6347,16 +6349,16 @@
         <v>6</v>
       </c>
       <c r="M15" s="43" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="N15" s="43"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="I16" s="88" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="K16" s="59">
         <v>135</v>
@@ -6366,25 +6368,22 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="9:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="9:12" x14ac:dyDescent="0.2">
       <c r="I17" s="90"/>
       <c r="J17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="K17" s="59" t="s">
         <v>439</v>
       </c>
-      <c r="K17" s="59" t="s">
-        <v>444</v>
-      </c>
       <c r="L17" s="60" t="s">
-        <v>444</v>
-      </c>
-      <c r="N17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="18" spans="9:14" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="18" spans="9:12" x14ac:dyDescent="0.2">
       <c r="I18" s="90"/>
       <c r="J18" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="K18" s="59">
         <v>134</v>
@@ -6413,7 +6412,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D139A1A-9547-BD45-8765-74E432024BF3}">
-  <dimension ref="A2:B18"/>
+  <dimension ref="A2:B15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -6422,117 +6421,112 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="72" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B2" s="72"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="39" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="39" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="39" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="39" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="39" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="39" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="39" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="39" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="39" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="39" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -6553,18 +6547,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6576,7 +6570,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6588,7 +6582,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6600,7 +6594,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -6612,7 +6606,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -6624,7 +6618,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6636,7 +6630,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6648,7 +6642,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6660,7 +6654,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -6672,7 +6666,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6684,7 +6678,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6696,7 +6690,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6708,7 +6702,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -6720,7 +6714,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -6732,7 +6726,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -6744,7 +6738,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6756,7 +6750,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6768,7 +6762,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -6780,7 +6774,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -6792,7 +6786,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -6804,7 +6798,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6816,7 +6810,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6828,7 +6822,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6840,7 +6834,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6852,7 +6846,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -6864,7 +6858,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6876,7 +6870,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -6888,7 +6882,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -6900,7 +6894,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -6912,7 +6906,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -6924,7 +6918,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -6936,7 +6930,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -6948,7 +6942,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -6960,7 +6954,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -6972,7 +6966,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -6984,7 +6978,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -6996,7 +6990,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -7008,7 +7002,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -7020,7 +7014,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -7032,7 +7026,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -7044,7 +7038,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -7056,7 +7050,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -7068,7 +7062,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -7080,7 +7074,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -7092,7 +7086,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -7104,7 +7098,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -7116,7 +7110,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -7128,7 +7122,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -7144,7 +7138,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
